--- a/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="152">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 8: Nullpunktsanalyse (V5)</t>
   </si>
@@ -146,18 +146,48 @@
     <t xml:space="preserve">a)  Dekningsbidraget per oppdrag, i kroner: prisen minus de variable kostnadene per oppdrag.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB per enhet = P − VEK (Økonomistyring 8.2, tabellen nr. 7; formelsamlingen kap. 8).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Nullpunktet i antall oppdrag: de faste kostnadene delt på dekningsbidraget per oppdrag. Et halvt oppdrag finnes ikke, så rund opp.</t>
   </si>
   <si>
+    <t xml:space="preserve">NPM = FTK / DB per enhet. Utledning: i nullpunktet er resultatet 0, så DB totalt = FTK, og DB per enhet × M = FTK (Økonomistyring 8.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Nullpunktet i kroner: de faste kostnadene ganger 100, delt på dekningsgraden i prosent. Regn først dekningsgraden (DB × 100 / P) med to desimaler.</t>
   </si>
   <si>
+    <t xml:space="preserve">DG = DB per enhet × 100 / P. NPO = FTK × 100 / DG (Økonomistyring 8.2, tabellen nr. 10 og 12, og utledningen av nullpunkt i kroner).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  En kollega regner nullpunktet i kroner slik: 2 100 000 × 100 / 7 300 = 28 767 kr. Hva har han gjort feil?   A: Han har brukt dekningsbidraget i kroner der dekningsgraden i prosent skal stå   B: Han har glemt å runde opp til hele oppdrag   C: Han har glemt merverdiavgiften på prisen   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Tom mener avdelingen bærer seg, fordi montørene har mye å gjøre. Hva svarer du ham? To setninger, med tall: resultatet ved 210 oppdrag, og hva som skal til.</t>
   </si>
   <si>
+    <t xml:space="preserve">Resultat = DB totalt − FTK (Økonomistyring 8.2, tabellen nr. 9). Salg under nullpunktet gir tap (8.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekkefølgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekningsbidraget først: 18 500 − 11 200. Så faste kostnader delt på det. Et halvt oppdrag finnes ikke: rund opp, også om desimalen er under 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kroner, ikke oppdrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekningsgraden er DB i prosent av prisen: 7 300 × 100 / 18 500. I kroner deler du på den, ikke på 7 300. Sjekk: svaret skal ligne 288 × 18 500.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.1 og 8.2 (nullpunkt i mengde og i kroner). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -218,12 +248,21 @@
     <t xml:space="preserve">a)  Dekningsbidraget per fakturerbar time, i kroner: det kunden betaler per time (timepris pluss materiell) minus den variable kostnaden per time (materiellinnkjøpet).</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet = P − VEK (Økonomistyring 8.2, tabellen nr. 7). Gjennomsnittspris og gjennomsnittskostnad per enhet når prisene varierer (8.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  De faste kostnadene i året, i kroner: alt som kommer uansett hvor mange timer som faktureres.</t>
   </si>
   <si>
+    <t xml:space="preserve">Faste kostnader er driftsuavhengige og påløper uansett hvor mye som produseres (Økonomistyring 8.1 og kap. 2.2.2). DB totalt = FTK + resultat (8.2, tabellen nr. 9).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Nullpunktet i fakturerbare timer: faste kostnader delt på dekningsbidraget per time. Rund opp til hele timer.</t>
   </si>
   <si>
+    <t xml:space="preserve">NPM = FTK / DB per enhet (Økonomistyring 8.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hvilke poster er variable kostnader i Fjell Elektros nullpunktsanalyse, med fakturerbar time som enhet? Spør for hver post: blir den mindre hvis det faktureres færre timer?</t>
   </si>
   <si>
@@ -248,6 +287,21 @@
     <t xml:space="preserve">e)  Mona fakturerer selv 700 timer. Hvor mange fakturerbare timer må hver av de to montørene ha for at Fjell Elektro skal gå i null, og hva betyr det for Mona som leder? To setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Nullpunktet i timer (8.2) fordelt på de som fakturerer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva kunden betaler per time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">890 kr for timen pluss 480 kr for materiellet. Det eneste som blir mindre med færre timer, er materiellinnkjøpet: 400 kr. DB = 1 370 − 400.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det som kommer uansett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lønnskostnaden (fast månedslønn), avskrivningene og andre driftskostnader. Kontroll: 3 500 × DB − FTK skal bli 144 240, budsjettets driftsresultat.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.1–8.2 (gjennomsnittspris og gjennomsnittskostnad per enhet). Faste og variable kostnader: kap. 2.2.2. Resultatbudsjettet: kap. 9 (OK09 A2).</t>
   </si>
   <si>
@@ -305,18 +359,42 @@
     <t xml:space="preserve">a)  Risikomarginen i prosent ved 320 oppdrag: (salgsinntekt − nullpunkt i kroner) × 100 / salgsinntekt. Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">RM (kr) = STI − NPO. RM (%) = RM (kr) × 100 / STI, eventuelt RM (M) × 100 / virkelig salgsmengde (Økonomistyring 8.2, tabellen nr. 13–15).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange oppdrag trengs for 300 000 kr i overskudd med uendret pris? Legg overskuddet til de faste kostnadene, del på DB og rund opp.</t>
   </si>
   <si>
+    <t xml:space="preserve">DB totalt = FTK + resultat (Økonomistyring 8.2, tabellen nr. 9). Antall for et gitt resultat = (FTK + ønsket resultat) / DB per enhet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Samme overskuddskrav, men prisen settes opp 8 % til 19 980 kr. Hvor mange oppdrag trengs nå? Rund opp.</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet = P − VEK (8.2). Eksempeloppgaven i 8.3: økt pris gir økt dekningsbidrag og dekningsgrad, lavere nullpunkt og større risikomargin.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Med de 210 oppdragene Tom har planlagt, er risikomarginen 210 − 288 = −78 oppdrag. Hva betyr det?   A: Avdelingen har en liten margin og tåler å miste 78 oppdrag   B: Avdelingen taper allerede penger og må skaffe 78 oppdrag til for å gå i null   C: Avdelingen ligger 78 oppdrag over kapasiteten   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Borettslaget vil ha 40 oppdrag til 15 % rabatt, altså 15 725 kr per oppdrag og 4 525 kr i dekningsbidrag. Skal Tom ta jobben? Regn resultatet med og uten avtalen, gi tre argumenter og si hvilken opplysning du mangler for å være sikker.</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet = P − VEK (8.2). Gjennomsnittspris når prisen varierer (8.1, kritikken av forutsetningene). Positivt dekningsbidrag øker resultatet så lenge de faste kostnadene er uendret (8.2, nr. 9).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risikomarginen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salgsinntekten ved 320: 320 × 18 500. Trekk fra nullpunktet i kroner, del på salgsinntekten, gang med 100. Sjekk i antall: 320 − 288.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overskudd og rabatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenk på overskuddet som en ekstra fast kostnad: 2 400 000 / DB. Borettslaget: 18 500 × 0,85 = 15 725; DB 4 525. Regn 280 oppdrag alene, så med de 40 i tillegg.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.2 (risikomargin; DB totalt = FTK + resultat) og 8.3 (endring i pris). Rabatt og gjennomsnittspris: avsnitt 8.1. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -365,16 +443,40 @@
     <t xml:space="preserve">a)  Risikomarginen i fakturerbare timer: budsjetterte timer minus nullpunktet i timer.</t>
   </si>
   <si>
+    <t xml:space="preserve">RM (M) = virkelig salgsmengde − salgsmengde i nullpunkt (Økonomistyring 8.2, tabellen nr. 13).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Risikomarginen i prosent: (salgsinntekt − nullpunkt i kroner) × 100 / salgsinntekt. Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">RM (kr) = STI − NPO. RM (%) = RM (kr) × 100 / STI, eventuelt RM (M) × 100 / virkelig salgsmengde (Økonomistyring 8.2, tabellen nr. 14–15).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Timeprisen settes opp 5 % til 934,50 kr; materiellet er uendret. Hva blir det nye nullpunktet i fakturerbare timer? Rund opp.</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet = P − VEK, NPM = FTK / DB per enhet (8.2). Økt pris gir lavere nullpunkt og større risikomargin (8.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona sier: «Risikomarginen er 4,2 %. Da tjener vi altså 4,2 % av det vi selger.» Hva betyr 4,2 % egentlig?   A: Ja: driftsresultatet er 4,2 % av salgsinntekten   B: Nei: salget kan falle 4,2 % før bedriften går i null   C: Nei: 4,2 % av timene er ikke fakturerbare   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Skal Mona sette timeprisen opp 5 %? Gi en anbefaling med tall. Regn gjerne hvor mange timer hun kan miste etter prisøkningen og fortsatt tjene like mye som i dag, og si hva nullpunktsanalysen ikke ser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antall for et gitt resultat = (FTK + resultat) / DB per enhet (8.2, nr. 9). Kritikken av forutsetningen om konstant pris (8.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timer: 3 500 − 3 352. Kroner: 4 795 000 − 4 591 280, delt på 4 795 000, ganger 100. De to prosentene blir nesten like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisen opp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare timeprisen øker: 890 × 1,05 = 934,50. Materiellet gir fortsatt 480 − 400 = 80 kr. Nytt DB = 934,50 + 80. Del de faste kostnadene på det.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.2 (risikomargin) og 8.3 (endring i pris). Resultatbudsjettet: kap. 9 (OK09 A2). Tallene bygger på oppgave A2.</t>
@@ -388,7 +490,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,8 +557,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,6 +597,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFFBF6EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -525,7 +667,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -574,11 +716,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -611,8 +773,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -640,7 +802,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -943,7 +1105,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1091,35 +1253,20 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11" t="str">
-        <f aca="false">IF(F16="","",IF(ABS(F16-(288))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="B16" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(5321845))&lt;=100,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
@@ -1127,72 +1274,176 @@
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="A","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F18="","",IF(ABS(F18-(288))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(5321845))&lt;=100,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="A","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="24">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1203,13 +1454,20 @@
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B16:G16"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:G22"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1226,7 +1484,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1237,7 +1495,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1247,7 +1505,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1258,7 +1516,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1282,10 +1540,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1295,10 +1553,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1308,10 +1566,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1321,10 +1579,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1334,10 +1592,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1347,10 +1605,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1360,10 +1618,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1388,7 +1646,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1400,187 +1658,276 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(3250760))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(3352))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(3250760))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(ABS(F23-(3352))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="11" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="11" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="11" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="32">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1593,19 +1940,26 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1622,7 +1976,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1633,7 +1987,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1643,7 +1997,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1654,7 +2008,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1678,10 +2032,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1694,7 +2048,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1704,10 +2058,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1717,10 +2071,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1730,10 +2084,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1743,10 +2097,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1756,10 +2110,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1772,7 +2126,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1797,7 +2151,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1809,108 +2163,197 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(329))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(274))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(329))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(274))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>115</v>
+      </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="27">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1924,13 +2367,20 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1947,7 +2397,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1958,7 +2408,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1968,7 +2418,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1979,7 +2429,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2006,7 +2456,7 @@
         <v>30</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2016,10 +2466,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2029,10 +2479,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2042,10 +2492,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2055,10 +2505,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2068,10 +2518,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2081,10 +2531,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2109,7 +2559,7 @@
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2121,108 +2571,197 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(4.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(3205))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F20="","",IF(ABS(F20-(4.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11" t="str">
+        <f aca="false">IF(F23="","",IF(ABS(F23-(3205))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>143</v>
+      </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="11" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="26">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2235,13 +2774,20 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
@@ -92,10 +92,10 @@
     <t xml:space="preserve">25 minutter · Helst alene. Sammen med sidemannen eller flere hvis du vil. Ark og blyant, appen (PC eller mobil) eller læreboka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Hvert oppdrag legger igjen et dekningsbidrag: pris minus variable kostnader per oppdrag (DB = P − VEK). Nullpunktet er salget der dekningsbidragene akkurat dekker de faste kostnadene. I antall: NPM = FTK / DB per enhet. I kroner: NPO = FTK × 100 / DG, der dekningsgraden DG = DB × 100 / P. Kontroll: nullpunktet i kroner er omtrent nullpunktet i antall ganger prisen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027; regnestykket er det samme uansett år. Tom Berg er driftsleder for serviceavdelingen i Nordlys, med fire montører og en lærling. To av montørene hans tar sikringsskapbytter, feilsøking og el-kontroller; regnestykket gjelder de oppdragene. Et oppdrag faktureres i snitt med 18 500 kr uten mva. Materiellet og montørtimene på akkurat den jobben koster 11 200 kr. Avdelingen bærer 2 100 000 kr i året i faste kostnader: verksted, servicebiler, forsikring og ledelse. Tom har planlagt 210 oppdrag neste år. Montørene har mye å gjøre, og Tom mener avdelingen bærer seg. Gå fram slik: dekningsbidraget per oppdrag først, så nullpunktet i antall, så dekningsgraden og nullpunktet i kroner. Til slutt: hva skal Kari si til Tom?</t>
+    <t xml:space="preserve">Kort oppsummert: Hvert oppdrag legger igjen et dekningsbidrag: pris minus variable kostnader per oppdrag (dekningsbidrag = pris − variable kostnader per enhet). Nullpunktet er salget der dekningsbidragene akkurat dekker de faste kostnadene. I antall: nullpunktet i antall = faste kostnader / dekningsbidrag per enhet. I kroner: nullpunktet i kroner = faste kostnader × 100 / dekningsgrad, der dekningsgraden = dekningsbidrag × 100 / pris. Kontroll: nullpunktet i kroner er omtrent nullpunktet i antall ganger prisen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casen er lagt til 2026/2027; regnestykket er det samme uansett år. Tom Berg er driftsleder for serviceavdelingen i Nordlys, med fire montører og en lærling. To av montørene hans tar sikringsskapbytter, feilsøking og el-kontroller; regnestykket gjelder de oppdragene. Et oppdrag faktureres i snitt med 18 500 kr uten merverdiavgift. Materiellet og montørtimene på akkurat den jobben koster 11 200 kr. Avdelingen bærer 2 100 000 kr i året i faste kostnader: verksted, servicebiler, forsikring og ledelse. Tom har planlagt 210 oppdrag neste år. Montørene har mye å gjøre, og Tom mener avdelingen bærer seg. Gå fram slik: dekningsbidraget per oppdrag først, så nullpunktet i antall, så dekningsgraden og nullpunktet i kroner. Til slutt: hva skal Kari si til Tom?</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">Verdi</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris per oppdrag (P)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 500 kr uten mva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable kostnader (VEK)</t>
+    <t xml:space="preserve">Pris per oppdrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 500 kr uten merverdiavgift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable kostnader</t>
   </si>
   <si>
     <t xml:space="preserve">11 200 kr per oppdrag: materiell og montørtimer på jobben</t>
   </si>
   <si>
-    <t xml:space="preserve">Faste kostnader (FTK)</t>
+    <t xml:space="preserve">Faste kostnader</t>
   </si>
   <si>
     <t xml:space="preserve">2 100 000 kr i året</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">Formel og begrep</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet = P − VEK (Økonomistyring 8.2, tabellen nr. 7; formelsamlingen kap. 8).</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet = pris − variable kostnader per enhet (Økonomistyring 8.2, tabellen nr. 7; formelsamlingen kap. 8).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Nullpunktet i antall oppdrag: de faste kostnadene delt på dekningsbidraget per oppdrag. Et halvt oppdrag finnes ikke, så rund opp.</t>
   </si>
   <si>
-    <t xml:space="preserve">NPM = FTK / DB per enhet. Utledning: i nullpunktet er resultatet 0, så DB totalt = FTK, og DB per enhet × M = FTK (Økonomistyring 8.2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)  Nullpunktet i kroner: de faste kostnadene ganger 100, delt på dekningsgraden i prosent. Regn først dekningsgraden (DB × 100 / P) med to desimaler.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG = DB per enhet × 100 / P. NPO = FTK × 100 / DG (Økonomistyring 8.2, tabellen nr. 10 og 12, og utledningen av nullpunkt i kroner).</t>
+    <t xml:space="preserve">Nullpunktet i antall = faste kostnader / dekningsbidrag per enhet. Utledning: i nullpunktet er resultatet 0, så sum dekningsbidrag = faste kostnader, og dekningsbidrag per enhet × antall = faste kostnader (Økonomistyring 8.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)  Nullpunktet i kroner: de faste kostnadene ganger 100, delt på dekningsgraden i prosent. Regn først dekningsgraden (dekningsbidrag × 100 / pris) med to desimaler.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekningsgrad = dekningsbidrag per enhet × 100 / pris. Nullpunktet i kroner = faste kostnader × 100 / dekningsgrad (Økonomistyring 8.2, tabellen nr. 10 og 12, og utledningen av nullpunkt i kroner).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  En kollega regner nullpunktet i kroner slik: 2 100 000 × 100 / 7 300 = 28 767 kr. Hva har han gjort feil?   A: Han har brukt dekningsbidraget i kroner der dekningsgraden i prosent skal stå   B: Han har glemt å runde opp til hele oppdrag   C: Han har glemt merverdiavgiften på prisen   (skriv bokstaven)</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">e)  Tom mener avdelingen bærer seg, fordi montørene har mye å gjøre. Hva svarer du ham? To setninger, med tall: resultatet ved 210 oppdrag, og hva som skal til.</t>
   </si>
   <si>
-    <t xml:space="preserve">Resultat = DB totalt − FTK (Økonomistyring 8.2, tabellen nr. 9). Salg under nullpunktet gir tap (8.1).</t>
+    <t xml:space="preserve">Resultat = sum dekningsbidrag − faste kostnader (Økonomistyring 8.2, tabellen nr. 9). Salg under nullpunktet gir tap (8.1).</t>
   </si>
   <si>
     <t xml:space="preserve">Hint, hvis du står fast</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">Kroner, ikke oppdrag</t>
   </si>
   <si>
-    <t xml:space="preserve">Dekningsgraden er DB i prosent av prisen: 7 300 × 100 / 18 500. I kroner deler du på den, ikke på 7 300. Sjekk: svaret skal ligne 288 × 18 500.</t>
+    <t xml:space="preserve">Dekningsgraden er dekningsbidrag i prosent av prisen: 7 300 × 100 / 18 500. I kroner deler du på den, ikke på 7 300. Sjekk: svaret skal ligne 288 × 18 500.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.1 og 8.2 (nullpunkt i mengde og i kroner). Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">Kort oppsummert: Nullpunktsanalysen trenger en enhet. I en installasjonsbedrift kan enheten være en fakturerbar time, med snittet av materiellet som følger timen (læreboka: gjennomsnittspris og gjennomsnittlig kostnad per enhet). Hva som er fast og variabelt, avhenger av bedriften: har montørene fast månedslønn, er lønna en fast kostnad. Nullpunkt = faste kostnader / dekningsbidrag per enhet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) har budsjettert 3 500 fakturerbare timer i første driftsår: to montører à 1 400 timer og eieren Mona Fjell 700 timer. Timeprisen er 890 kr uten mva. Materiellet følger timene: i snitt kjøpes det inn for 400 kr per fakturerbar time, og det selges videre med 20 % påslag, altså for 480 kr. Montørene og Mona har fast månedslønn, så lønnskostnaden på 2 671 760 kr (lønn + 46,8 % sosiale kostnader) kommer uansett hvor mange timer som faktureres. I tillegg kommer avskrivninger på 60 000 kr og andre driftskostnader på 519 000 kr. Resultatbudsjettet viser et driftsresultat på 144 240 kr. Regn ut dekningsbidraget per fakturerbar time, de faste kostnadene og nullpunktet i timer.</t>
+    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) har budsjettert 3 500 fakturerbare timer i første driftsår: to montører à 1 400 timer og eieren Mona Fjell 700 timer. Timeprisen er 890 kr uten merverdiavgift. Materiellet følger timene: i snitt kjøpes det inn for 400 kr per fakturerbar time, og det selges videre med 20 % påslag, altså for 480 kr. Montørene og Mona har fast månedslønn, så lønnskostnaden på 2 671 760 kr (lønn + 46,8 % sosiale kostnader) kommer uansett hvor mange timer som faktureres. I tillegg kommer avskrivninger på 60 000 kr og andre driftskostnader på 519 000 kr. Resultatbudsjettet viser et driftsresultat på 144 240 kr. Regn ut dekningsbidraget per fakturerbar time, de faste kostnadene og nullpunktet i timer.</t>
   </si>
   <si>
     <t xml:space="preserve">Fakturerbare timer</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">a)  Dekningsbidraget per fakturerbar time, i kroner: det kunden betaler per time (timepris pluss materiell) minus den variable kostnaden per time (materiellinnkjøpet).</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet = P − VEK (Økonomistyring 8.2, tabellen nr. 7). Gjennomsnittspris og gjennomsnittskostnad per enhet når prisene varierer (8.1).</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet = pris − variable kostnader per enhet (Økonomistyring 8.2, tabellen nr. 7). Gjennomsnittspris og gjennomsnittskostnad per enhet når prisene varierer (8.1).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  De faste kostnadene i året, i kroner: alt som kommer uansett hvor mange timer som faktureres.</t>
   </si>
   <si>
-    <t xml:space="preserve">Faste kostnader er driftsuavhengige og påløper uansett hvor mye som produseres (Økonomistyring 8.1 og kap. 2.2.2). DB totalt = FTK + resultat (8.2, tabellen nr. 9).</t>
+    <t xml:space="preserve">Faste kostnader er driftsuavhengige og påløper uansett hvor mye som produseres (Økonomistyring 8.1 og kap. 2.2.2). Sum dekningsbidrag = faste kostnader + resultat (8.2, tabellen nr. 9).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Nullpunktet i fakturerbare timer: faste kostnader delt på dekningsbidraget per time. Rund opp til hele timer.</t>
   </si>
   <si>
-    <t xml:space="preserve">NPM = FTK / DB per enhet (Økonomistyring 8.2).</t>
+    <t xml:space="preserve">Nullpunktet i antall = faste kostnader / dekningsbidrag per enhet (Økonomistyring 8.2).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Hvilke poster er variable kostnader i Fjell Elektros nullpunktsanalyse, med fakturerbar time som enhet? Spør for hver post: blir den mindre hvis det faktureres færre timer?</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">Hva kunden betaler per time</t>
   </si>
   <si>
-    <t xml:space="preserve">890 kr for timen pluss 480 kr for materiellet. Det eneste som blir mindre med færre timer, er materiellinnkjøpet: 400 kr. DB = 1 370 − 400.</t>
+    <t xml:space="preserve">890 kr for timen pluss 480 kr for materiellet. Det eneste som blir mindre med færre timer, er materiellinnkjøpet: 400 kr. Dekningsbidrag = 1 370 − 400.</t>
   </si>
   <si>
     <t xml:space="preserve">Det som kommer uansett</t>
   </si>
   <si>
-    <t xml:space="preserve">Lønnskostnaden (fast månedslønn), avskrivningene og andre driftskostnader. Kontroll: 3 500 × DB − FTK skal bli 144 240, budsjettets driftsresultat.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.1–8.2 (gjennomsnittspris og gjennomsnittskostnad per enhet). Faste og variable kostnader: kap. 2.2.2. Resultatbudsjettet: kap. 9 (OK09 A2).</t>
+    <t xml:space="preserve">Lønnskostnaden (fast månedslønn), avskrivningene og andre driftskostnader. Kontroll: 3 500 × dekningsbidrag − faste kostnader skal bli 144 240, budsjettets driftsresultat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.1–8.2 (gjennomsnittspris og gjennomsnittskostnad per enhet). Faste og variable kostnader: kap. 2.2.2. Resultatbudsjettet: kap. 9 (oppgave A2 der).</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: risikomargin, overskuddskrav og borettslagets rabatt</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Risikomarginen er avstanden fra planlagt salg ned til nullpunktet, i antall, kroner eller prosent: RM (%) = (STI − NPO) × 100 / STI. Er den negativ, taper avdelingen allerede penger. Skal avdelingen gi et overskudd, legges overskuddet til de faste kostnadene før du deler på DB, fordi DB totalt = FTK + resultat. En prisøkning går rett inn i dekningsbidraget.</t>
+    <t xml:space="preserve">Kort oppsummert: Risikomarginen er avstanden fra planlagt salg ned til nullpunktet, i antall, kroner eller prosent: risikomargin i prosent = (sum inntekter − nullpunktet i kroner) × 100 / sum inntekter. Er den negativ, taper avdelingen allerede penger. Skal avdelingen gi et overskudd, legges overskuddet til de faste kostnadene før du deler på dekningsbidraget, fordi sum dekningsbidrag = faste kostnader + resultat. En prisøkning går rett inn i dekningsbidraget.</t>
   </si>
   <si>
     <t xml:space="preserve">Casen er lagt til 2026/2027. Serviceavdelingen har nullpunkt på 288 oppdrag (5 321 918 kr med uavrundet dekningsgrad), og Tom har planlagt 210. Kari mener løsningen er å selge mer: hun vil ha avdelingen opp i 320 oppdrag til full pris, og hun krever 300 000 kr i overskudd. Hun spør også hva som skjer hvis prisen settes opp 8 %. Samtidig ligger et tilbud på Toms bord: et borettslag vil ha el-kontroll i 40 leiligheter, men krever 15 % rabatt. Uten avtalen ligger avdelingen an til 280 oppdrag til full pris. Gå fram slik: risikomarginen ved 320, så antall oppdrag for overskuddskravet med og uten prisøkning, så borettslaget.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris, variable, DB per oppdrag</t>
+    <t xml:space="preserve">Pris, variable, dekningsbidrag</t>
   </si>
   <si>
     <t xml:space="preserve">18 500 · 11 200 · 7 300 kr</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">a)  Risikomarginen i prosent ved 320 oppdrag: (salgsinntekt − nullpunkt i kroner) × 100 / salgsinntekt. Én desimal.</t>
   </si>
   <si>
-    <t xml:space="preserve">RM (kr) = STI − NPO. RM (%) = RM (kr) × 100 / STI, eventuelt RM (M) × 100 / virkelig salgsmengde (Økonomistyring 8.2, tabellen nr. 13–15).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b)  Hvor mange oppdrag trengs for 300 000 kr i overskudd med uendret pris? Legg overskuddet til de faste kostnadene, del på DB og rund opp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB totalt = FTK + resultat (Økonomistyring 8.2, tabellen nr. 9). Antall for et gitt resultat = (FTK + ønsket resultat) / DB per enhet.</t>
+    <t xml:space="preserve">Risikomargin i kroner = sum inntekter − nullpunktet i kroner. Risikomargin i prosent = risikomargin i kroner × 100 / sum inntekter, eventuelt risikomargin i antall × 100 / virkelig salgsmengde (Økonomistyring 8.2, tabellen nr. 13–15).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b)  Hvor mange oppdrag trengs for 300 000 kr i overskudd med uendret pris? Legg overskuddet til de faste kostnadene, del på dekningsbidrag og rund opp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum dekningsbidrag = faste kostnader + resultat (Økonomistyring 8.2, tabellen nr. 9). Antall for et gitt resultat = (faste kostnader + ønsket resultat) / dekningsbidrag per enhet.</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Samme overskuddskrav, men prisen settes opp 8 % til 19 980 kr. Hvor mange oppdrag trengs nå? Rund opp.</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet = P − VEK (8.2). Eksempeloppgaven i 8.3: økt pris gir økt dekningsbidrag og dekningsgrad, lavere nullpunkt og større risikomargin.</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet = pris − variable kostnader per enhet (8.2). Eksempeloppgaven i 8.3: økt pris gir økt dekningsbidrag og dekningsgrad, lavere nullpunkt og større risikomargin.</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Med de 210 oppdragene Tom har planlagt, er risikomarginen 210 − 288 = −78 oppdrag. Hva betyr det?   A: Avdelingen har en liten margin og tåler å miste 78 oppdrag   B: Avdelingen taper allerede penger og må skaffe 78 oppdrag til for å gå i null   C: Avdelingen ligger 78 oppdrag over kapasiteten   (skriv bokstaven)</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">e)  Borettslaget vil ha 40 oppdrag til 15 % rabatt, altså 15 725 kr per oppdrag og 4 525 kr i dekningsbidrag. Skal Tom ta jobben? Regn resultatet med og uten avtalen, gi tre argumenter og si hvilken opplysning du mangler for å være sikker.</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet = P − VEK (8.2). Gjennomsnittspris når prisen varierer (8.1, kritikken av forutsetningene). Positivt dekningsbidrag øker resultatet så lenge de faste kostnadene er uendret (8.2, nr. 9).</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet = pris − variable kostnader per enhet (8.2). Gjennomsnittspris når prisen varierer (8.1, kritikken av forutsetningene). Positivt dekningsbidrag øker resultatet så lenge de faste kostnadene er uendret (8.2, nr. 9).</t>
   </si>
   <si>
     <t xml:space="preserve">Risikomarginen</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">Overskudd og rabatt</t>
   </si>
   <si>
-    <t xml:space="preserve">Tenk på overskuddet som en ekstra fast kostnad: 2 400 000 / DB. Borettslaget: 18 500 × 0,85 = 15 725; DB 4 525. Regn 280 oppdrag alene, så med de 40 i tillegg.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.2 (risikomargin; DB totalt = FTK + resultat) og 8.3 (endring i pris). Rabatt og gjennomsnittspris: avsnitt 8.1. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Tenk på overskuddet som en ekstra fast kostnad: 2 400 000 / dekningsbidrag. Borettslaget: 18 500 × 0,85 = 15 725; dekningsbidrag 4 525. Regn 280 oppdrag alene, så med de 40 i tillegg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.2 (risikomargin; sum dekningsbidrag = faste kostnader + resultat) og 8.3 (endring i pris). Rabatt og gjennomsnittspris: avsnitt 8.1. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B2 · Din egen el-bedrift: hvor mye tåler Fjell Elektro?</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">Kort oppsummert: Risikomarginen kan regnes i enheter (her fakturerbare timer), i kroner og i prosent. Den sier hvor mye salget kan falle før bedriften går i null. Den er ikke det samme som driftsmarginen, som sier hvor stor del av salget som blir overskudd. En prisøkning går rett inn i dekningsbidraget og senker nullpunktet mest, men analysen sier ingenting om hvor mange kunder som sier nei.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS har faste kostnader på 3 250 760 kr og 970 kr i dekningsbidrag per fakturerbar time (oppgave A2). Nullpunktet er 3 352 timer, eller 4 591 280 kr i salgsinntekt. Budsjettet er 3 500 timer og 4 795 000 kr. Mona synes marginen ser tynn ut. Hun vurderer å sette timeprisen opp 5 %, fra 890 til 934,50 kr uten mva; materiellet selges som før. Kundene er boligkunder og små næringskunder i Oslo øst, og bedriften har ingen faste rammeavtaler. Regn ut risikomarginen i timer og i prosent, og nullpunktet etter en prisøkning.</t>
+    <t xml:space="preserve">Fjell Elektro AS har faste kostnader på 3 250 760 kr og 970 kr i dekningsbidrag per fakturerbar time (oppgave A2). Nullpunktet er 3 352 timer, eller 4 591 280 kr i salgsinntekt. Budsjettet er 3 500 timer og 4 795 000 kr. Mona synes marginen ser tynn ut. Hun vurderer å sette timeprisen opp 5 %, fra 890 til 934,50 kr uten merverdiavgift; materiellet selges som før. Kundene er boligkunder og små næringskunder i Oslo øst, og bedriften har ingen faste rammeavtaler. Regn ut risikomarginen i timer og i prosent, og nullpunktet etter en prisøkning.</t>
   </si>
   <si>
     <t xml:space="preserve">3 250 760 kr</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per fakturerbar time</t>
+    <t xml:space="preserve">Dekningsbidrag per time</t>
   </si>
   <si>
     <t xml:space="preserve">970 kr (1 370 − 400)</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">a)  Risikomarginen i fakturerbare timer: budsjetterte timer minus nullpunktet i timer.</t>
   </si>
   <si>
-    <t xml:space="preserve">RM (M) = virkelig salgsmengde − salgsmengde i nullpunkt (Økonomistyring 8.2, tabellen nr. 13).</t>
+    <t xml:space="preserve">Risikomargin i antall = virkelig salgsmengde − salgsmengde i nullpunkt (Økonomistyring 8.2, tabellen nr. 13).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Risikomarginen i prosent: (salgsinntekt − nullpunkt i kroner) × 100 / salgsinntekt. Én desimal.</t>
   </si>
   <si>
-    <t xml:space="preserve">RM (kr) = STI − NPO. RM (%) = RM (kr) × 100 / STI, eventuelt RM (M) × 100 / virkelig salgsmengde (Økonomistyring 8.2, tabellen nr. 14–15).</t>
+    <t xml:space="preserve">Risikomargin i kroner = sum inntekter − nullpunktet i kroner. Risikomargin i prosent = risikomargin i kroner × 100 / sum inntekter, eventuelt risikomargin i antall × 100 / virkelig salgsmengde (Økonomistyring 8.2, tabellen nr. 14–15).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Timeprisen settes opp 5 % til 934,50 kr; materiellet er uendret. Hva blir det nye nullpunktet i fakturerbare timer? Rund opp.</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet = P − VEK, NPM = FTK / DB per enhet (8.2). Økt pris gir lavere nullpunkt og større risikomargin (8.3).</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet = pris − variable kostnader per enhet, nullpunktet i antall = faste kostnader / dekningsbidrag per enhet (8.2). Økt pris gir lavere nullpunkt og større risikomargin (8.3).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Mona sier: «Risikomarginen er 4,2 %. Da tjener vi altså 4,2 % av det vi selger.» Hva betyr 4,2 % egentlig?   A: Ja: driftsresultatet er 4,2 % av salgsinntekten   B: Nei: salget kan falle 4,2 % før bedriften går i null   C: Nei: 4,2 % av timene er ikke fakturerbare   (skriv bokstaven)</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">e)  Skal Mona sette timeprisen opp 5 %? Gi en anbefaling med tall. Regn gjerne hvor mange timer hun kan miste etter prisøkningen og fortsatt tjene like mye som i dag, og si hva nullpunktsanalysen ikke ser.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antall for et gitt resultat = (FTK + resultat) / DB per enhet (8.2, nr. 9). Kritikken av forutsetningen om konstant pris (8.1).</t>
+    <t xml:space="preserve">Antall for et gitt resultat = (faste kostnader + resultat) / dekningsbidrag per enhet (8.2, nr. 9). Kritikken av forutsetningen om konstant pris (8.1).</t>
   </si>
   <si>
     <t xml:space="preserve">Marginen</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">Prisen opp</t>
   </si>
   <si>
-    <t xml:space="preserve">Bare timeprisen øker: 890 × 1,05 = 934,50. Materiellet gir fortsatt 480 − 400 = 80 kr. Nytt DB = 934,50 + 80. Del de faste kostnadene på det.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.2 (risikomargin) og 8.3 (endring i pris). Resultatbudsjettet: kap. 9 (OK09 A2). Tallene bygger på oppgave A2.</t>
+    <t xml:space="preserve">Bare timeprisen øker: 890 × 1,05 = 934,50. Materiellet gir fortsatt 480 − 400 = 80 kr. Nytt dekningsbidrag = 934,50 + 80. Del de faste kostnadene på det.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 8, avsnitt 8.2 (risikomargin) og 8.3 (endring i pris). Resultatbudsjettet: kap. 9 (oppgave A2 der). Tallene bygger på oppgave A2.</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
         <v>40</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
         <v>40</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
         <v>40</v>
       </c>
@@ -1904,7 +1904,7 @@
       <c r="F42" s="18"/>
       <c r="G42" s="18"/>
     </row>
-    <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
         <v>92</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>94</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
         <v>40</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
         <v>40</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
         <v>40</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
         <v>40</v>
       </c>

--- a/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="152">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 8: Nullpunktsanalyse (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 8: Nullpunktsanalyse (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok08/OK08_Klasseoppgaver_v5.xlsx
@@ -200,7 +200,7 @@
     <t xml:space="preserve">Kort oppsummert: Nullpunktsanalysen trenger en enhet. I en installasjonsbedrift kan enheten være en fakturerbar time, med snittet av materiellet som følger timen (læreboka: gjennomsnittspris og gjennomsnittlig kostnad per enhet). Hva som er fast og variabelt, avhenger av bedriften: har montørene fast månedslønn, er lønna en fast kostnad. Nullpunkt = faste kostnader / dekningsbidrag per enhet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) har budsjettert 3 500 fakturerbare timer i første driftsår: to montører à 1 400 timer og eieren Mona Fjell 700 timer. Timeprisen er 890 kr uten merverdiavgift. Materiellet følger timene: i snitt kjøpes det inn for 400 kr per fakturerbar time, og det selges videre med 20 % påslag, altså for 480 kr. Montørene og Mona har fast månedslønn, så lønnskostnaden på 2 671 760 kr (lønn + 46,8 % sosiale kostnader) kommer uansett hvor mange timer som faktureres. I tillegg kommer avskrivninger på 60 000 kr og andre driftskostnader på 519 000 kr. Resultatbudsjettet viser et driftsresultat på 144 240 kr. Regn ut dekningsbidraget per fakturerbar time, de faste kostnadene og nullpunktet i timer.</t>
+    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) har budsjettert 3 500 fakturerbare timer i første driftsår: to montører à 1 400 timer og eieren Mona Fjell 700 timer. Timeprisen er 890 kr uten merverdiavgift. Materiellet følger timene: i snitt kjøpes det inn for 400 kr per fakturerbar time (materiellkjøpet 1 400 000 kr delt på 3 500 timer), og det selges videre med 20 % påslag, altså for 480 kr. Montørene og Mona har fast månedslønn, så lønnskostnaden på 2 671 760 kr (lønn 2 × 560 000 + 700 000 = 1 820 000 kr, pluss 46,8 % sosiale kostnader) kommer uansett hvor mange timer som faktureres. I tillegg kommer avskrivninger på 60 000 kr og andre driftskostnader på 519 000 kr. Resultatbudsjettet viser et driftsresultat på 144 240 kr. Regn ut dekningsbidraget per fakturerbar time, de faste kostnadene og nullpunktet i timer.</t>
   </si>
   <si>
     <t xml:space="preserve">Fakturerbare timer</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">Per fakturerbar time</t>
   </si>
   <si>
-    <t xml:space="preserve">Timepris 890 kr + materiell solgt for 480 kr</t>
+    <t xml:space="preserve">Timepris 890 kr + materiell solgt for 400 × 1,20 = 480 kr</t>
   </si>
   <si>
     <t xml:space="preserve">Variabel kostnad</t>
   </si>
   <si>
-    <t xml:space="preserve">Materiell, 400 kr innkjøp per time</t>
+    <t xml:space="preserve">Materiell: 1 400 000 / 3 500 = 400 kr per time</t>
   </si>
   <si>
     <t xml:space="preserve">Lønnskostnad</t>
   </si>
   <si>
-    <t xml:space="preserve">2 671 760 kr, fast månedslønn</t>
+    <t xml:space="preserve">1 820 000 × 1,468 = 2 671 760 kr, fast månedslønn</t>
   </si>
   <si>
     <t xml:space="preserve">Avskrivninger</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">Prisen opp 8 %</t>
   </si>
   <si>
-    <t xml:space="preserve">19 980 kr per oppdrag</t>
+    <t xml:space="preserve">18 500 × 1,08 = 19 980 kr per oppdrag</t>
   </si>
   <si>
     <t xml:space="preserve">Borettslaget</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">Kort oppsummert: Risikomarginen kan regnes i enheter (her fakturerbare timer), i kroner og i prosent. Den sier hvor mye salget kan falle før bedriften går i null. Den er ikke det samme som driftsmarginen, som sier hvor stor del av salget som blir overskudd. En prisøkning går rett inn i dekningsbidraget og senker nullpunktet mest, men analysen sier ingenting om hvor mange kunder som sier nei.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS har faste kostnader på 3 250 760 kr og 970 kr i dekningsbidrag per fakturerbar time (oppgave A2). Nullpunktet er 3 352 timer, eller 4 591 280 kr i salgsinntekt. Budsjettet er 3 500 timer og 4 795 000 kr. Mona synes marginen ser tynn ut. Hun vurderer å sette timeprisen opp 5 %, fra 890 til 934,50 kr uten merverdiavgift; materiellet selges som før. Kundene er boligkunder og små næringskunder i Oslo øst, og bedriften har ingen faste rammeavtaler. Regn ut risikomarginen i timer og i prosent, og nullpunktet etter en prisøkning.</t>
+    <t xml:space="preserve">Fjell Elektro AS har faste kostnader på 3 250 760 kr og 970 kr i dekningsbidrag per fakturerbar time (oppgave A2). Nullpunktet er 3 352 timer, eller 3 352 × 1 370 = 4 591 280 kr i salgsinntekt (1 370 kr er timepris 890 + materiell 480). Budsjettet er 3 500 timer og 3 500 × 1 370 = 4 795 000 kr. Mona synes marginen ser tynn ut. Hun vurderer å sette timeprisen opp 5 %, fra 890 til 934,50 kr uten merverdiavgift; materiellet selges som før. Kundene er boligkunder og små næringskunder i Oslo øst, og bedriften har ingen faste rammeavtaler. Regn ut risikomarginen i timer og i prosent, og nullpunktet etter en prisøkning.</t>
   </si>
   <si>
     <t xml:space="preserve">3 250 760 kr</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">970 kr (1 370 − 400)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 352 timer = 4 591 280 kr</t>
+    <t xml:space="preserve">3 352 timer × 1 370 = 4 591 280 kr</t>
   </si>
   <si>
     <t xml:space="preserve">Budsjett</t>
   </si>
   <si>
-    <t xml:space="preserve">3 500 timer = 4 795 000 kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144 240 kr (driftsmargin 3,0 %)</t>
+    <t xml:space="preserve">3 500 timer × 1 370 = 4 795 000 kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144 240 kr (144 240 / 4 795 000 = 3,0 %)</t>
   </si>
   <si>
     <t xml:space="preserve">Timepris opp 5 %</t>
@@ -1514,7 +1514,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>58</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>126</v>
       </c>
